--- a/115年7月預劃匯入版.xlsx
+++ b/115年7月預劃匯入版.xlsx
@@ -1753,12 +1753,12 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="12"/>
+      <c r="K16" s="14" t="s">
         <v>7</v>
-      </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12" t="s">
-        <v>10</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
@@ -1795,7 +1795,7 @@
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
       <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
+      <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>

--- a/115年7月預劃匯入版.xlsx
+++ b/115年7月預劃匯入版.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="48">
   <si>
     <t>員編
 ID No.</t>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>張芯瑜</t>
+  </si>
+  <si>
+    <t>r</t>
   </si>
   <si>
     <t>T02612</t>
@@ -593,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -684,19 +687,25 @@
     <xf borderId="25" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="26" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="26" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="27" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="28" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="26" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="29" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1874,23 +1883,23 @@
       <c r="C19" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>10</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>7</v>
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
@@ -1916,85 +1925,85 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="16"/>
-      <c r="B20" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="31" t="s">
+      <c r="B20" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32" t="s">
+      <c r="C20" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="33"/>
-      <c r="V20" s="33"/>
-      <c r="W20" s="34"/>
-      <c r="X20" s="32"/>
-      <c r="Y20" s="32" t="s">
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="36"/>
+      <c r="Y20" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="Z20" s="33"/>
-      <c r="AA20" s="33"/>
-      <c r="AB20" s="33"/>
-      <c r="AC20" s="33"/>
-      <c r="AD20" s="33"/>
+      <c r="Z20" s="34"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="34"/>
+      <c r="AC20" s="34"/>
+      <c r="AD20" s="34"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="16"/>
-      <c r="B21" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="36" t="s">
+      <c r="B21" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38" t="s">
+      <c r="C21" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="39"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="O21" s="38"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="39"/>
-      <c r="X21" s="37" t="s">
+      <c r="O21" s="40"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="Y21" s="37" t="s">
+      <c r="Y21" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="Z21" s="38"/>
-      <c r="AA21" s="38"/>
-      <c r="AB21" s="38"/>
-      <c r="AC21" s="38"/>
-      <c r="AD21" s="38" t="s">
+      <c r="Z21" s="40"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="40"/>
+      <c r="AC21" s="40"/>
+      <c r="AD21" s="40" t="s">
         <v>10</v>
       </c>
     </row>

--- a/115年7月預劃匯入版.xlsx
+++ b/115年7月預劃匯入版.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="48">
   <si>
     <t>員編
 ID No.</t>
@@ -596,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -624,6 +624,9 @@
     <xf borderId="8" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -643,6 +646,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -689,6 +695,12 @@
     </xf>
     <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -943,7 +955,7 @@
     <col customWidth="1" min="1" max="1" width="5.33"/>
     <col customWidth="1" min="2" max="2" width="12.11"/>
     <col customWidth="1" min="3" max="3" width="16.67"/>
-    <col customWidth="1" min="4" max="30" width="16.78"/>
+    <col customWidth="1" min="4" max="31" width="16.78"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -1035,6 +1047,9 @@
       <c r="AD1" s="4">
         <v>46234.0</v>
       </c>
+      <c r="AE1" s="4">
+        <v>46235.0</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="5"/>
@@ -1150,862 +1165,894 @@
         <f t="shared" si="1"/>
         <v>a</v>
       </c>
+      <c r="AE2" s="9"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="12" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Y3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="17"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="13" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AA4" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB4" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC4" s="13" t="s">
+      <c r="AA4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="AD4" s="13"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="17"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="17"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
+      <c r="F6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="17"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="16"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="19" t="s">
+      <c r="E7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q7" s="19" t="s">
+      <c r="L7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="19" t="s">
+      <c r="R7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="S7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
+      <c r="S7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="17"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="17"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="16"/>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="14"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="15"/>
+      <c r="AE9" s="17"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13" t="s">
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="W10" s="13" t="s">
+      <c r="W10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="X10" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y10" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
+      <c r="X10" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y10" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="17"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="13" t="s">
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="W11" s="13" t="s">
+      <c r="W11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="X11" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y11" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z11" s="23"/>
-      <c r="AA11" s="23"/>
-      <c r="AB11" s="23"/>
-      <c r="AC11" s="23"/>
-      <c r="AD11" s="23"/>
+      <c r="X11" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="17"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="25" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="J12" s="27" t="s">
+      <c r="D12" s="29"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K12" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
-      <c r="S12" s="28" t="s">
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="T12" s="28"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="28"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="27"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="28"/>
-      <c r="AB12" s="28"/>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="28"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="17"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="13"/>
-      <c r="AB13" s="13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13" s="13"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE13" s="17"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17" t="s">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12" t="s">
+      <c r="L14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="Z14" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="13"/>
-      <c r="AC14" s="13"/>
-      <c r="AD14" s="13"/>
+      <c r="S14" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA14" s="14"/>
+      <c r="AB14" s="14"/>
+      <c r="AC14" s="14"/>
+      <c r="AD14" s="14"/>
+      <c r="AE14" s="17"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="16"/>
-      <c r="B15" s="20" t="s">
+      <c r="A15" s="18"/>
+      <c r="B15" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="12" t="s">
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="Y15" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z15" s="13" t="s">
+      <c r="Y15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z15" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
+      <c r="AA15" s="14"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="14"/>
+      <c r="AD15" s="14"/>
+      <c r="AE15" s="17"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="12" t="s">
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="14" t="s">
+      <c r="J16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="13"/>
-      <c r="AA16" s="13"/>
-      <c r="AB16" s="13"/>
-      <c r="AC16" s="13"/>
-      <c r="AD16" s="13"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="14"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="14"/>
+      <c r="AD16" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE16" s="17"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13" t="s">
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12" t="s">
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="Z17" s="13" t="s">
+      <c r="Z17" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
+      <c r="AA17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="17"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17" t="s">
+      <c r="A18" s="18"/>
+      <c r="B18" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="R18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="13"/>
-      <c r="AB18" s="13"/>
-      <c r="AC18" s="13"/>
-      <c r="AD18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+      <c r="AE18" s="17"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="H19" s="30" t="s">
+      <c r="F19" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
-      <c r="AD19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="14"/>
+      <c r="AE19" s="32" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="16"/>
-      <c r="B20" s="31" t="s">
+      <c r="A20" s="18"/>
+      <c r="B20" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36" t="s">
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="36" t="s">
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="40"/>
+      <c r="Y20" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="Z20" s="34"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="34"/>
-      <c r="AC20" s="34"/>
-      <c r="AD20" s="34"/>
+      <c r="Z20" s="38"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="38"/>
+      <c r="AC20" s="38"/>
+      <c r="AD20" s="38"/>
+      <c r="AE20" s="17"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="16"/>
-      <c r="B21" s="37" t="s">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40" t="s">
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="O21" s="40"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="39"/>
-      <c r="R21" s="39"/>
-      <c r="S21" s="40"/>
-      <c r="T21" s="40"/>
-      <c r="U21" s="40"/>
-      <c r="V21" s="40"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="39" t="s">
+      <c r="O21" s="44"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="45"/>
+      <c r="X21" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="Y21" s="39" t="s">
+      <c r="Y21" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="Z21" s="40"/>
-      <c r="AA21" s="40"/>
-      <c r="AB21" s="40"/>
-      <c r="AC21" s="40"/>
-      <c r="AD21" s="40" t="s">
+      <c r="Z21" s="44"/>
+      <c r="AA21" s="44"/>
+      <c r="AB21" s="44"/>
+      <c r="AC21" s="44"/>
+      <c r="AD21" s="44" t="s">
         <v>10</v>
       </c>
+      <c r="AE21" s="17"/>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>

--- a/115年7月預劃匯入版.xlsx
+++ b/115年7月預劃匯入版.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="48">
   <si>
     <t>員編
 ID No.</t>
@@ -1714,12 +1714,8 @@
       <c r="O14" s="14"/>
       <c r="P14" s="15"/>
       <c r="Q14" s="13"/>
-      <c r="R14" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="S14" s="34" t="s">
-        <v>10</v>
-      </c>
+      <c r="R14" s="33"/>
+      <c r="S14" s="34"/>
       <c r="T14" s="14"/>
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>

--- a/115年7月預劃匯入版.xlsx
+++ b/115年7月預劃匯入版.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="60">
   <si>
     <t>員編
 ID No.</t>
@@ -46,6 +46,9 @@
     <t>林金緗</t>
   </si>
   <si>
+    <t>r</t>
+  </si>
+  <si>
     <t>r'</t>
   </si>
   <si>
@@ -83,6 +86,12 @@
   </si>
   <si>
     <t>潘元浩</t>
+  </si>
+  <si>
+    <t>01夜B1</t>
+  </si>
+  <si>
+    <t>01夜B2</t>
   </si>
   <si>
     <t>T02505</t>
@@ -160,19 +169,46 @@
     <t>張芯瑜</t>
   </si>
   <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>T02612</t>
-  </si>
-  <si>
-    <t>蕭曉琦</t>
-  </si>
-  <si>
     <t>T02613</t>
   </si>
   <si>
     <t>張雅荃</t>
+  </si>
+  <si>
+    <t>T02758</t>
+  </si>
+  <si>
+    <t>王映心</t>
+  </si>
+  <si>
+    <t>T02762</t>
+  </si>
+  <si>
+    <t>周怡萍</t>
+  </si>
+  <si>
+    <t>T02763</t>
+  </si>
+  <si>
+    <t>陳佑融</t>
+  </si>
+  <si>
+    <t>T02769</t>
+  </si>
+  <si>
+    <t>吳東翰</t>
+  </si>
+  <si>
+    <t>T02776</t>
+  </si>
+  <si>
+    <t>陳怡臻</t>
+  </si>
+  <si>
+    <t>T02777</t>
+  </si>
+  <si>
+    <t>彭裕涵</t>
   </si>
 </sst>
 </file>
@@ -207,7 +243,7 @@
       <name val="Microsoft JhengHei"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,8 +262,14 @@
         <bgColor rgb="FFE5E5E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="41">
     <border/>
     <border>
       <left style="medium">
@@ -517,14 +559,32 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -533,11 +593,46 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <left style="medium">
@@ -549,7 +644,65 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -560,35 +713,19 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -596,7 +733,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="64">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -669,6 +806,12 @@
     <xf borderId="19" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="20" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -693,53 +836,111 @@
     <xf borderId="25" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="12" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="26" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="27" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="28" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="28" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="26" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="29" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="26" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="30" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="26" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="31" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="27" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="32" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="17" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="34" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="17" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="27" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="18" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="35" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="36" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="37" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="37" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="38" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="39" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="40" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -952,10 +1153,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.33"/>
-    <col customWidth="1" min="2" max="2" width="12.11"/>
-    <col customWidth="1" min="3" max="3" width="16.67"/>
-    <col customWidth="1" min="4" max="31" width="16.78"/>
+    <col customWidth="1" min="1" max="1" width="4.22"/>
+    <col customWidth="1" min="2" max="2" width="9.44"/>
+    <col customWidth="1" min="3" max="3" width="12.89"/>
+    <col customWidth="1" min="4" max="31" width="13.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -1167,7 +1368,7 @@
       </c>
       <c r="AE2" s="9"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="24.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1214,7 +1415,7 @@
       <c r="AD3" s="14"/>
       <c r="AE3" s="17"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="24.75" customHeight="1">
       <c r="A4" s="18"/>
       <c r="B4" s="19" t="s">
         <v>8</v>
@@ -1236,10 +1437,14 @@
       <c r="O4" s="14"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
+      <c r="R4" s="21" t="s">
+        <v>7</v>
+      </c>
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
+      <c r="U4" s="14" t="s">
+        <v>10</v>
+      </c>
       <c r="V4" s="14"/>
       <c r="W4" s="15"/>
       <c r="X4" s="13"/>
@@ -1254,18 +1459,18 @@
         <v>6</v>
       </c>
       <c r="AC4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD4" s="14"/>
       <c r="AE4" s="17"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="24.75" customHeight="1">
       <c r="A5" s="18"/>
       <c r="B5" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="14"/>
@@ -1304,16 +1509,16 @@
       <c r="AD5" s="14"/>
       <c r="AE5" s="17"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="24.75" customHeight="1">
       <c r="A6" s="18"/>
       <c r="B6" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>7</v>
@@ -1351,13 +1556,13 @@
       <c r="AD6" s="14"/>
       <c r="AE6" s="17"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="24.75" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>7</v>
@@ -1378,7 +1583,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" s="21" t="s">
         <v>7</v>
@@ -1399,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R7" s="21" t="s">
         <v>7</v>
@@ -1420,13 +1625,13 @@
       <c r="AD7" s="14"/>
       <c r="AE7" s="17"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="24.75" customHeight="1">
       <c r="A8" s="18"/>
       <c r="B8" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="14"/>
@@ -1446,7 +1651,7 @@
         <v>7</v>
       </c>
       <c r="S8" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
@@ -1461,50 +1666,50 @@
       <c r="AD8" s="14"/>
       <c r="AE8" s="17"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="24.75" customHeight="1">
       <c r="A9" s="18"/>
       <c r="B9" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
       <c r="O9" s="14"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="14"/>
       <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="15"/>
-      <c r="AE9" s="17"/>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="24.75" customHeight="1">
       <c r="A10" s="18"/>
       <c r="B10" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="14"/>
@@ -1517,10 +1722,18 @@
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
       <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
+      <c r="O10" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" s="24" t="s">
+        <v>25</v>
+      </c>
       <c r="S10" s="14"/>
       <c r="T10" s="14"/>
       <c r="U10" s="14"/>
@@ -1528,7 +1741,7 @@
         <v>7</v>
       </c>
       <c r="W10" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X10" s="13" t="s">
         <v>6</v>
@@ -1541,126 +1754,138 @@
       <c r="AB10" s="14"/>
       <c r="AC10" s="14"/>
       <c r="AD10" s="14"/>
-      <c r="AE10" s="17"/>
+      <c r="AE10" s="17" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="24.75" customHeight="1">
       <c r="A11" s="18"/>
       <c r="B11" s="22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
+      <c r="Q11" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="S11" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="T11" s="27"/>
+      <c r="U11" s="27"/>
       <c r="V11" s="14" t="s">
         <v>7</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="X11" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="X11" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="Y11" s="24" t="s">
+      <c r="Y11" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="17"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="17" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="24.75" customHeight="1">
       <c r="A12" s="18"/>
-      <c r="B12" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="29"/>
+      <c r="B12" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="31"/>
       <c r="E12" s="14"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="31" t="s">
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="K12" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="29"/>
+      <c r="J12" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="32"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="31"/>
       <c r="Y12" s="13"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="30"/>
+      <c r="Z12" s="32"/>
+      <c r="AA12" s="32"/>
+      <c r="AB12" s="32"/>
+      <c r="AC12" s="32"/>
+      <c r="AD12" s="32"/>
       <c r="AE12" s="17"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="24.75" customHeight="1">
       <c r="A13" s="18"/>
       <c r="B13" s="19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>7</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="21" t="s">
         <v>7</v>
@@ -1683,21 +1908,25 @@
       <c r="AA13" s="14"/>
       <c r="AB13" s="14"/>
       <c r="AC13" s="14"/>
-      <c r="AD13" s="32" t="s">
+      <c r="AD13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="AE13" s="17"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="24.75" customHeight="1">
       <c r="A14" s="18"/>
       <c r="B14" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
@@ -1714,8 +1943,12 @@
       <c r="O14" s="14"/>
       <c r="P14" s="15"/>
       <c r="Q14" s="13"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="34"/>
+      <c r="R14" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="S14" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="T14" s="14"/>
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
@@ -1733,13 +1966,13 @@
       <c r="AD14" s="14"/>
       <c r="AE14" s="17"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="24.75" customHeight="1">
       <c r="A15" s="18"/>
       <c r="B15" s="22" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="14"/>
@@ -1776,16 +2009,16 @@
       <c r="AD15" s="14"/>
       <c r="AE15" s="17"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="24.75" customHeight="1">
       <c r="A16" s="18"/>
       <c r="B16" s="19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>7</v>
@@ -1794,10 +2027,10 @@
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
       <c r="I16" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>7</v>
@@ -1820,18 +2053,18 @@
       <c r="AA16" s="14"/>
       <c r="AB16" s="14"/>
       <c r="AC16" s="14"/>
-      <c r="AD16" s="32" t="s">
+      <c r="AD16" s="14" t="s">
         <v>7</v>
       </c>
       <c r="AE16" s="17"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="24.75" customHeight="1">
       <c r="A17" s="18"/>
       <c r="B17" s="19" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
@@ -1850,7 +2083,7 @@
       <c r="R17" s="13"/>
       <c r="S17" s="14"/>
       <c r="T17" s="14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
@@ -1860,7 +2093,7 @@
         <v>7</v>
       </c>
       <c r="Z17" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA17" s="14"/>
       <c r="AB17" s="14"/>
@@ -1868,13 +2101,13 @@
       <c r="AD17" s="14"/>
       <c r="AE17" s="17"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="24.75" customHeight="1">
       <c r="A18" s="18"/>
       <c r="B18" s="19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="14"/>
@@ -1913,19 +2146,19 @@
       <c r="AD18" s="14"/>
       <c r="AE18" s="17"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="24.75" customHeight="1">
       <c r="A19" s="18"/>
       <c r="B19" s="19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>43</v>
+      <c r="E19" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>6</v>
@@ -1933,11 +2166,11 @@
       <c r="G19" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="32" t="s">
-        <v>29</v>
+      <c r="H19" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
@@ -1960,101 +2193,307 @@
       <c r="AB19" s="14"/>
       <c r="AC19" s="14"/>
       <c r="AD19" s="14"/>
-      <c r="AE19" s="32" t="s">
+      <c r="AE19" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="24.75" customHeight="1">
       <c r="A20" s="18"/>
-      <c r="B20" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="40"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="39"/>
-      <c r="X20" s="40"/>
-      <c r="Y20" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z20" s="38"/>
-      <c r="AA20" s="38"/>
-      <c r="AB20" s="38"/>
-      <c r="AC20" s="38"/>
-      <c r="AD20" s="38"/>
+      <c r="B20" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="38"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="O20" s="39"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="39"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="40"/>
+      <c r="X20" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y20" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z20" s="39"/>
+      <c r="AA20" s="39"/>
+      <c r="AB20" s="39"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="AE20" s="17"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="18"/>
+    <row r="21" ht="24.75" customHeight="1">
       <c r="B21" s="41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21" s="43"/>
       <c r="E21" s="44"/>
       <c r="F21" s="44"/>
       <c r="G21" s="44"/>
       <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="43"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
-      <c r="N21" s="44" t="s">
-        <v>7</v>
-      </c>
+      <c r="N21" s="44"/>
       <c r="O21" s="44"/>
       <c r="P21" s="45"/>
-      <c r="Q21" s="43"/>
+      <c r="Q21" s="46" t="s">
+        <v>7</v>
+      </c>
       <c r="R21" s="43"/>
       <c r="S21" s="44"/>
       <c r="T21" s="44"/>
-      <c r="U21" s="44"/>
+      <c r="U21" s="44" t="s">
+        <v>7</v>
+      </c>
       <c r="V21" s="44"/>
-      <c r="W21" s="45"/>
-      <c r="X21" s="43" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y21" s="43" t="s">
-        <v>10</v>
-      </c>
+      <c r="W21" s="44"/>
+      <c r="X21" s="47"/>
+      <c r="Y21" s="43"/>
       <c r="Z21" s="44"/>
       <c r="AA21" s="44"/>
       <c r="AB21" s="44"/>
       <c r="AC21" s="44"/>
       <c r="AD21" s="44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" ht="24.75" customHeight="1">
+      <c r="B22" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="50"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="AE21" s="17"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="24"/>
+      <c r="U22" s="24"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="24"/>
+      <c r="AD22" s="24"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="23" ht="24.75" customHeight="1">
+      <c r="B23" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="R23" s="43"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="V23" s="44"/>
+      <c r="W23" s="44"/>
+      <c r="X23" s="47"/>
+      <c r="Y23" s="43"/>
+      <c r="Z23" s="44"/>
+      <c r="AA23" s="44"/>
+      <c r="AB23" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC23" s="44"/>
+      <c r="AD23" s="44"/>
+    </row>
+    <row r="24" ht="24.75" customHeight="1">
+      <c r="B24" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="57"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="M24" s="58"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="57"/>
+      <c r="S24" s="58"/>
+      <c r="T24" s="58"/>
+      <c r="U24" s="58"/>
+      <c r="V24" s="58"/>
+      <c r="W24" s="58"/>
+      <c r="X24" s="61"/>
+      <c r="Y24" s="57"/>
+      <c r="Z24" s="58"/>
+      <c r="AA24" s="58"/>
+      <c r="AB24" s="58"/>
+      <c r="AC24" s="58"/>
+      <c r="AD24" s="58"/>
+    </row>
+    <row r="25" ht="24.75" customHeight="1">
+      <c r="B25" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="50"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="52"/>
+      <c r="R25" s="50"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="24"/>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="53"/>
+      <c r="Y25" s="50"/>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="24"/>
+      <c r="AB25" s="24"/>
+      <c r="AC25" s="24"/>
+      <c r="AD25" s="24"/>
+    </row>
+    <row r="26" ht="24.75" customHeight="1">
+      <c r="B26" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="43"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="44"/>
+      <c r="X26" s="47"/>
+      <c r="Y26" s="43"/>
+      <c r="Z26" s="44"/>
+      <c r="AA26" s="44"/>
+      <c r="AB26" s="44"/>
+      <c r="AC26" s="44"/>
+      <c r="AD26" s="44"/>
+    </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
@@ -3033,8 +3472,68 @@
   <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A3:A21"/>
+    <mergeCell ref="A3:A20"/>
   </mergeCells>
+  <conditionalFormatting sqref="E21:E26">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(E21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21:D26 F21:I21 F22:K23 F24:I26 K21">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(D21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L21:O26">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(L21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q21:AA21">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(Q21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P21">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(P21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB21:AD21">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(AB21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q22:AA23">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(Q22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P22:P23">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(P22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB22:AD23">
+    <cfRule type="containsText" dxfId="0" priority="9" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(AB22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q24:AA26">
+    <cfRule type="containsText" dxfId="0" priority="10" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(Q24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P24:P26">
+    <cfRule type="containsText" dxfId="0" priority="11" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(P24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB24:AD26">
+    <cfRule type="containsText" dxfId="0" priority="12" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH(("r"),(AB24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>

--- a/115年7月預劃匯入版.xlsx
+++ b/115年7月預劃匯入版.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="60">
   <si>
     <t>員編
 ID No.</t>
@@ -812,10 +812,10 @@
     <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="20" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="21" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1740,16 +1740,16 @@
       <c r="V10" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="W10" s="14" t="s">
-        <v>11</v>
+      <c r="W10" s="13" t="s">
+        <v>6</v>
       </c>
       <c r="X10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="Y10" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z10" s="14"/>
+      <c r="Y10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z10" s="26"/>
       <c r="AA10" s="14"/>
       <c r="AB10" s="14"/>
       <c r="AC10" s="14"/>
@@ -1766,18 +1766,18 @@
       <c r="C11" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
       <c r="I11" s="28"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
       <c r="P11" s="21" t="s">
         <v>24</v>
       </c>
@@ -1787,28 +1787,26 @@
       <c r="R11" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="S11" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="26"/>
+      <c r="U11" s="26"/>
       <c r="V11" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="W11" s="14" t="s">
+      <c r="W11" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="X11" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="X11" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y11" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z11" s="27"/>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="27"/>
-      <c r="AC11" s="27"/>
-      <c r="AD11" s="27"/>
+      <c r="Z11" s="26"/>
+      <c r="AA11" s="26"/>
+      <c r="AB11" s="26"/>
+      <c r="AC11" s="26"/>
+      <c r="AD11" s="26"/>
       <c r="AE11" s="17" t="s">
         <v>7</v>
       </c>
